--- a/settings.xlsx
+++ b/settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sh0tny1\рабочий стол\Yerlan\Автоматизация отчета в 1С\Код автоматизации\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE57B6D8-FD76-4C31-9C9C-8CE39BE3D61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C49618-7BDA-40EC-B391-74D38829A9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
